--- a/MainTop/09.07.2026 Имена популярное/print.xlsx
+++ b/MainTop/09.07.2026 Имена популярное/print.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\09.07.2026 Имена популярное\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA77B22-672B-4E30-9DCB-D40CF7C4E623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3862D7FD-3D55-4FD9-AE9C-59AEE441D4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -535,25 +535,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -564,8 +564,11 @@
         <f>B2/16</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -573,11 +576,14 @@
         <v>80</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C56" si="0">B3/16</f>
+        <f t="shared" ref="C3:D56" si="0">B3/16</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -588,8 +594,11 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -600,8 +609,11 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -612,8 +624,11 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -624,8 +639,11 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -636,8 +654,11 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -648,8 +669,11 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -660,8 +684,11 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -672,8 +699,11 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -684,8 +714,11 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -696,8 +729,11 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -708,8 +744,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -720,8 +759,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -732,8 +774,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -744,8 +789,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
@@ -756,8 +804,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -768,8 +819,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -780,8 +834,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
@@ -792,8 +849,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
@@ -804,8 +864,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -816,8 +879,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
@@ -828,8 +894,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
@@ -840,8 +909,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -852,8 +924,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
@@ -864,8 +939,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
@@ -876,8 +954,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
@@ -888,8 +969,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
@@ -900,8 +984,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>31</v>
       </c>
@@ -912,8 +999,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
@@ -924,8 +1014,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
@@ -936,8 +1029,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
@@ -948,8 +1044,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
@@ -960,8 +1059,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -972,8 +1074,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
@@ -984,8 +1089,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
@@ -996,8 +1104,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
@@ -1008,8 +1119,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
@@ -1020,8 +1134,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>41</v>
       </c>
@@ -1032,8 +1149,11 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
@@ -1044,8 +1164,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
@@ -1056,8 +1179,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
@@ -1068,8 +1194,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
@@ -1080,8 +1209,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -1092,8 +1224,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
@@ -1104,8 +1239,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
@@ -1116,8 +1254,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
@@ -1128,8 +1269,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
@@ -1140,8 +1284,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
@@ -1152,8 +1299,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
@@ -1164,8 +1314,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
@@ -1176,8 +1329,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
@@ -1188,8 +1344,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
@@ -1200,8 +1359,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
@@ -1211,6 +1373,9 @@
       <c r="C56">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
